--- a/modele-devis.xlsx
+++ b/modele-devis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1291de943bb811bd/Bureau/dev/JBAdeV/wishlist-devis-plugin/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\levin\OneDrive\Bureau\dev\JBAdeV\wishlist-devis-plugin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:8000000b_{2AF9E974-4404-4F60-8EAE-586D7E0E9FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F30A63-BEEA-4E4F-883A-7E2EAAC9CABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="623" xr2:uid="{8866F9C9-3E05-4079-AF79-A2DC14F902F9}"/>
   </bookViews>
@@ -184,8 +184,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00\ [$€-1]"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ [$€-1]"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -412,46 +412,46 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -461,184 +461,169 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="4" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -779,7 +764,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{909E8E84-426E-40dd-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
+            <a14:hiddenFill xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
               <a:blipFill dpi="0" rotWithShape="0">
                 <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
                 <a:srcRect/>
@@ -790,7 +775,7 @@
             </a14:hiddenFill>
           </a:ext>
           <a:ext uri="{91240B29-F687-4f45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" w="9525" cap="flat">
+            <a14:hiddenLine xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cap="flat">
               <a:solidFill>
                 <a:srgbClr val="808080"/>
               </a:solidFill>
@@ -800,7 +785,7 @@
             </a14:hiddenLine>
           </a:ext>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
+            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="000000">
@@ -863,7 +848,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{909E8E84-426E-40dd-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
+            <a14:hiddenFill xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
               <a:blipFill dpi="0" rotWithShape="0">
                 <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
                 <a:srcRect/>
@@ -874,7 +859,7 @@
             </a14:hiddenFill>
           </a:ext>
           <a:ext uri="{91240B29-F687-4f45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" w="9525" cap="flat">
+            <a14:hiddenLine xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cap="flat">
               <a:solidFill>
                 <a:srgbClr val="808080"/>
               </a:solidFill>
@@ -884,7 +869,7 @@
             </a14:hiddenLine>
           </a:ext>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
+            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="000000">
@@ -1208,7 +1193,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
+            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="000000">
@@ -1252,7 +1237,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
+            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="000000">
@@ -1289,203 +1274,203 @@
     <col min="10" max="16384" width="8.77734375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="80" customFormat="1" ht="31.05" customHeight="1">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:13" s="3" customFormat="1" ht="31.05" customHeight="1">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="53"/>
-    </row>
-    <row r="2" spans="1:13" s="59" customFormat="1" ht="16.05" customHeight="1">
-      <c r="A2" s="54" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="48"/>
+    </row>
+    <row r="2" spans="1:13" s="54" customFormat="1" ht="16.05" customHeight="1">
+      <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-    </row>
-    <row r="3" spans="1:13" s="59" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A3" s="57" t="s">
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+    </row>
+    <row r="3" spans="1:13" s="54" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="57"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="62"/>
-    </row>
-    <row r="4" spans="1:13" s="59" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A4" s="57" t="s">
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="57"/>
+    </row>
+    <row r="4" spans="1:13" s="54" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="57" t="s">
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="63"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="62"/>
-    </row>
-    <row r="5" spans="1:13" s="59" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A5" s="58" t="s">
+      <c r="E4" s="58"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="57"/>
+    </row>
+    <row r="5" spans="1:13" s="54" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A5" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="57" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="63"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="62"/>
-    </row>
-    <row r="6" spans="1:13" s="59" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A6" s="58" t="s">
+      <c r="E5" s="58"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="57"/>
+    </row>
+    <row r="6" spans="1:13" s="54" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A6" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="57" t="s">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="60"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="62"/>
-    </row>
-    <row r="7" spans="1:13" s="59" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A7" s="58" t="s">
+      <c r="F6" s="55"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="57"/>
+    </row>
+    <row r="7" spans="1:13" s="54" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A7" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="57"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="62"/>
-    </row>
-    <row r="8" spans="1:13" s="59" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="47" t="s">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="52"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="57"/>
+    </row>
+    <row r="8" spans="1:13" s="54" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A8" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="57"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="52"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="65" t="s">
+      <c r="F8" s="55"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="60" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="59" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A9" s="47"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="57"/>
+    <row r="9" spans="1:13" s="54" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A9" s="45"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="52"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="65"/>
-    </row>
-    <row r="10" spans="1:13" s="59" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A10" s="66"/>
-      <c r="B10" s="67" t="s">
+      <c r="F9" s="55"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="60"/>
+    </row>
+    <row r="10" spans="1:13" s="54" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A10" s="61"/>
+      <c r="B10" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="69" t="s">
+      <c r="C10" s="63"/>
+      <c r="D10" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="73" t="s">
+      <c r="E10" s="65"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="68" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="59" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A11" s="66"/>
-      <c r="B11" s="67" t="s">
+    <row r="11" spans="1:13" s="54" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A11" s="61"/>
+      <c r="B11" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="75"/>
-    </row>
-    <row r="12" spans="1:13" s="82" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A12" s="76" t="s">
+      <c r="C11" s="69"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="70"/>
+    </row>
+    <row r="12" spans="1:13" s="75" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A12" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76" t="s">
+      <c r="B12" s="72"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="76" t="s">
+      <c r="H12" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="78" t="s">
+      <c r="I12" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="81"/>
-    </row>
-    <row r="13" spans="1:13" s="82" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A13" s="76" t="s">
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:13" s="75" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A13" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="77" t="s">
+      <c r="B13" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="76" t="s">
+      <c r="C13" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="76" t="s">
+      <c r="D13" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="76" t="s">
+      <c r="E13" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="76" t="s">
+      <c r="F13" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="76"/>
-      <c r="H13" s="76" t="s">
+      <c r="G13" s="71"/>
+      <c r="H13" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="79" t="s">
+      <c r="I13" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="81"/>
+      <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:13" s="14" customFormat="1" ht="13.95" customHeight="1">
       <c r="A14" s="10"/>
@@ -1510,7 +1495,6 @@
       <c r="G15" s="16"/>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
-      <c r="J15" s="45"/>
     </row>
     <row r="16" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="18" t="s">
@@ -1525,7 +1509,7 @@
         <v>23</v>
       </c>
       <c r="I16" s="24"/>
-      <c r="J16" s="46"/>
+      <c r="J16" s="25"/>
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
@@ -1546,7 +1530,7 @@
         <f>I16*5%</f>
         <v>0</v>
       </c>
-      <c r="J17" s="46"/>
+      <c r="J17" s="25"/>
       <c r="K17" s="25"/>
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
@@ -1567,7 +1551,7 @@
         <f>(I16+I17)*20%</f>
         <v>0</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="25"/>
       <c r="K18" s="25"/>
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
@@ -1581,14 +1565,14 @@
       <c r="D19" s="20"/>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
-      <c r="H19" s="83" t="s">
+      <c r="H19" s="76" t="s">
         <v>28</v>
       </c>
       <c r="I19" s="27">
         <f>SUM(I16:I18)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="46"/>
+      <c r="J19" s="25"/>
       <c r="K19" s="25"/>
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>

--- a/modele-devis.xlsx
+++ b/modele-devis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\levin\OneDrive\Bureau\dev\JBAdeV\wishlist-devis-plugin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F30A63-BEEA-4E4F-883A-7E2EAAC9CABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FFBB47-7B67-4080-A7BF-4E7233F0F2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="623" xr2:uid="{8866F9C9-3E05-4079-AF79-A2DC14F902F9}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="Excel_BuiltIn__FilterDatabase" localSheetId="0">order!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>JB AdeV, créations depuis 1993</t>
   </si>
@@ -71,39 +71,15 @@
     <t>date:</t>
   </si>
   <si>
-    <t>ref</t>
-  </si>
-  <si>
     <t>qu.</t>
   </si>
   <si>
     <t>prix</t>
   </si>
   <si>
-    <t>€</t>
-  </si>
-  <si>
-    <t>créateur</t>
-  </si>
-  <si>
-    <t>désignation</t>
-  </si>
-  <si>
-    <t>collection</t>
-  </si>
-  <si>
-    <t>finition</t>
-  </si>
-  <si>
-    <t>dimensions</t>
-  </si>
-  <si>
     <t>unit.</t>
   </si>
   <si>
-    <t>total</t>
-  </si>
-  <si>
     <t>conditions de vente:</t>
   </si>
   <si>
@@ -131,36 +107,9 @@
     <t>suivant l' usage acompte en votre aimable règlement:</t>
   </si>
   <si>
-    <t>RIB:</t>
-  </si>
-  <si>
-    <t>bénéficiaire: Jean-Baptiste Astier de Villatte</t>
-  </si>
-  <si>
-    <t>banque: Crédit Agricole du Finistère</t>
-  </si>
-  <si>
-    <t>Agence du Guilvinec (00040)</t>
-  </si>
-  <si>
     <t>code IBAN: FR76 1290 6000 4057 4655 8576 747</t>
   </si>
   <si>
-    <t>code BIC: AGRIFRPP829</t>
-  </si>
-  <si>
-    <t>code banque: 12906</t>
-  </si>
-  <si>
-    <t>code guichet: 00040</t>
-  </si>
-  <si>
-    <t>n° de compte: 57465585767</t>
-  </si>
-  <si>
-    <t>clé RIB: 47</t>
-  </si>
-  <si>
     <t xml:space="preserve">En cas de retard de paiement, seront exigibles, conformément à l'article L 441-6 du code de commerce, une indemnité calculée </t>
   </si>
   <si>
@@ -177,6 +126,12 @@
   </si>
   <si>
     <t>Acompte:</t>
+  </si>
+  <si>
+    <t>total €</t>
+  </si>
+  <si>
+    <t>Ref., Désignation, finition et dimensions</t>
   </si>
 </sst>
 </file>
@@ -187,7 +142,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ [$€-1]"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -251,11 +206,6 @@
       <name val="Didot"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="10"/>
-      <name val="Didot"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color indexed="10"/>
       <name val="Didot"/>
@@ -332,13 +282,6 @@
       <family val="3"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <name val="Arial"/>
@@ -351,7 +294,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -388,6 +331,12 @@
         <bgColor indexed="55"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -436,108 +385,84 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -564,22 +489,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -601,30 +514,64 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="4" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -718,16 +665,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>170180</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1075193</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>6096</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1047008</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>12723</xdr:rowOff>
+      <xdr:colOff>926592</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>187431</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -751,8 +698,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3949700" y="571500"/>
-          <a:ext cx="1168400" cy="1308100"/>
+          <a:off x="3227081" y="597408"/>
+          <a:ext cx="1332727" cy="1266423"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -764,7 +711,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{909E8E84-426E-40dd-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:blipFill dpi="0" rotWithShape="0">
                 <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
                 <a:srcRect/>
@@ -775,7 +722,7 @@
             </a14:hiddenFill>
           </a:ext>
           <a:ext uri="{91240B29-F687-4f45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cap="flat">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" w="9525" cap="flat">
               <a:solidFill>
                 <a:srgbClr val="808080"/>
               </a:solidFill>
@@ -785,7 +732,7 @@
             </a14:hiddenLine>
           </a:ext>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="000000">
@@ -809,7 +756,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>5072</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>170205</xdr:rowOff>
     </xdr:to>
@@ -848,7 +795,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{909E8E84-426E-40dd-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:blipFill dpi="0" rotWithShape="0">
                 <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
                 <a:srcRect/>
@@ -859,7 +806,7 @@
             </a14:hiddenFill>
           </a:ext>
           <a:ext uri="{91240B29-F687-4f45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cap="flat">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" w="9525" cap="flat">
               <a:solidFill>
                 <a:srgbClr val="808080"/>
               </a:solidFill>
@@ -869,7 +816,7 @@
             </a14:hiddenLine>
           </a:ext>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="000000">
@@ -1193,7 +1140,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="000000">
@@ -1237,7 +1184,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="000000">
@@ -1259,1025 +1206,907 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126BE42E-CCE8-49BB-9B09-F66ECF2D2A9C}">
-  <dimension ref="A1:M99"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="29" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18" style="3" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="5" customWidth="1"/>
     <col min="7" max="7" width="7.44140625" style="6" customWidth="1"/>
     <col min="8" max="8" width="8.109375" style="7" customWidth="1"/>
     <col min="9" max="9" width="14.77734375" style="7" customWidth="1"/>
     <col min="10" max="16384" width="8.77734375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" ht="31.05" customHeight="1">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:9" s="3" customFormat="1" ht="31.05" customHeight="1">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="47"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="39"/>
       <c r="F1" s="2"/>
       <c r="G1" s="6"/>
       <c r="H1" s="7"/>
-      <c r="I1" s="48"/>
-    </row>
-    <row r="2" spans="1:13" s="54" customFormat="1" ht="16.05" customHeight="1">
-      <c r="A2" s="49" t="s">
+      <c r="I1" s="40"/>
+    </row>
+    <row r="2" spans="1:9" s="46" customFormat="1" ht="16.05" customHeight="1">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-    </row>
-    <row r="3" spans="1:13" s="54" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A3" s="52" t="s">
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+    </row>
+    <row r="3" spans="1:9" s="46" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A3" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="52"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="57"/>
-    </row>
-    <row r="4" spans="1:13" s="54" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A4" s="52" t="s">
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="47"/>
+    </row>
+    <row r="4" spans="1:9" s="46" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A4" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="58"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="57"/>
-    </row>
-    <row r="5" spans="1:13" s="54" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="47"/>
+    </row>
+    <row r="5" spans="1:9" s="46" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A5" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="52" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="57"/>
-    </row>
-    <row r="6" spans="1:13" s="54" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="47"/>
+    </row>
+    <row r="6" spans="1:9" s="46" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A6" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="52" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="55"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="57"/>
-    </row>
-    <row r="7" spans="1:13" s="54" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A7" s="53" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="47"/>
+    </row>
+    <row r="7" spans="1:9" s="46" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A7" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="52"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="57"/>
-    </row>
-    <row r="8" spans="1:13" s="54" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="45" t="s">
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="47"/>
+    </row>
+    <row r="8" spans="1:9" s="46" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A8" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="60" t="s">
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="48" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="54" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A9" s="45"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="60"/>
-    </row>
-    <row r="10" spans="1:13" s="54" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A10" s="61"/>
-      <c r="B10" s="62" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="64" t="s">
+    <row r="9" spans="1:9" s="46" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A9" s="37"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="48"/>
+    </row>
+    <row r="10" spans="1:9" s="46" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A10" s="49"/>
+      <c r="B10" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="51"/>
+      <c r="D10" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="68" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="54" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A11" s="61"/>
-      <c r="B11" s="62" t="s">
+      <c r="E10" s="53"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="46" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A11" s="49"/>
+      <c r="B11" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="69"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="70"/>
-    </row>
-    <row r="12" spans="1:13" s="75" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A12" s="71" t="s">
+      <c r="C11" s="57"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="58"/>
+    </row>
+    <row r="12" spans="1:9" s="11" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A12" s="61"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="63"/>
+    </row>
+    <row r="13" spans="1:9" s="11" customFormat="1" ht="13.95" customHeight="1">
+      <c r="A13" s="61"/>
+      <c r="B13" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="71" t="s">
+      <c r="H13" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="73" t="s">
+      <c r="I13" s="64" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="11" customFormat="1" ht="48" customHeight="1">
+      <c r="A14" s="66"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="4.95" customHeight="1">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
+    </row>
+    <row r="16" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="A16" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="14"/>
-    </row>
-    <row r="13" spans="1:13" s="75" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A13" s="71" t="s">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="H16" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="71" t="s">
+      <c r="I16" s="19"/>
+    </row>
+    <row r="17" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="A17" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="71" t="s">
+      <c r="B17" s="20"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="H17" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="71" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="71" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="14"/>
-    </row>
-    <row r="14" spans="1:13" s="14" customFormat="1" ht="13.95" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="4.95" customHeight="1">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-    </row>
-    <row r="16" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A16" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="H16" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="24"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-    </row>
-    <row r="17" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A17" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="H17" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="13">
+      <c r="I17" s="10">
         <f>I16*5%</f>
         <v>0</v>
       </c>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-    </row>
-    <row r="18" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A18" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="H18" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="13">
+    </row>
+    <row r="18" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="A18" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="H18" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="10">
         <f>(I16+I17)*20%</f>
         <v>0</v>
       </c>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-    </row>
-    <row r="19" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A19" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="H19" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="27">
+    </row>
+    <row r="19" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="A19" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="H19" s="59" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="21">
         <f>SUM(I16:I18)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-    </row>
-    <row r="20" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A20" s="26" t="s">
+    </row>
+    <row r="20" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="A20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="H20" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="H20" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I20" s="13">
+      <c r="I20" s="10">
         <v>0</v>
       </c>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-    </row>
-    <row r="21" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
+    </row>
+    <row r="21" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="6"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="H21" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="33">
+      <c r="B21" s="23"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="H21" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="27">
         <f>I19*50%</f>
         <v>0</v>
       </c>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-    </row>
-    <row r="22" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A22" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-    </row>
-    <row r="23" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A23" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="34"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-    </row>
-    <row r="24" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A24" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="H24" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="13"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-    </row>
-    <row r="25" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A25" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="H25" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="28"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-    </row>
-    <row r="26" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A26" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
-    </row>
-    <row r="27" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A27" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
-    </row>
-    <row r="28" spans="1:13" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A28" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
-    </row>
-    <row r="29" spans="1:13" ht="15" customHeight="1">
-      <c r="A29" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="10"/>
-      <c r="J29"/>
-      <c r="K29"/>
-      <c r="L29"/>
-      <c r="M29"/>
-    </row>
-    <row r="30" spans="1:13" ht="15" customHeight="1">
-      <c r="A30" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="36"/>
+    </row>
+    <row r="22" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="A22" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+    </row>
+    <row r="23" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="A23" s="60"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+    </row>
+    <row r="24" spans="1:9" ht="15" customHeight="1">
+      <c r="A24" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="9"/>
+    </row>
+    <row r="25" spans="1:9" ht="15" customHeight="1">
+      <c r="A25" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="9"/>
+    </row>
+    <row r="26" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="A26" s="60"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+    </row>
+    <row r="27" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="A27" s="60"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+    </row>
+    <row r="28" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="A28" s="60"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+    </row>
+    <row r="29" spans="1:9" ht="15" customHeight="1">
+      <c r="A29" s="60"/>
+      <c r="B29" s="60"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="9"/>
+    </row>
+    <row r="30" spans="1:9" ht="15" customHeight="1">
+      <c r="A30" s="60"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="29"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="10"/>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30"/>
-      <c r="M30"/>
-    </row>
-    <row r="31" spans="1:13" ht="15" customHeight="1">
-      <c r="A31" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="36"/>
+      <c r="G30" s="9"/>
+    </row>
+    <row r="31" spans="1:9" ht="15" customHeight="1">
+      <c r="A31" s="60"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="29"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="10"/>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31"/>
-      <c r="M31"/>
-    </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1">
-      <c r="A32" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="10"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32"/>
-      <c r="M32"/>
-    </row>
-    <row r="33" spans="1:13" ht="15" customHeight="1">
-      <c r="A33" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="10"/>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
-    </row>
-    <row r="34" spans="1:13" ht="15" customHeight="1">
-      <c r="A34" s="10"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="G34" s="10"/>
-      <c r="I34" s="23"/>
-    </row>
-    <row r="35" spans="1:13" ht="15" customHeight="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="G35" s="10"/>
-      <c r="I35" s="23"/>
-    </row>
-    <row r="36" spans="1:13" ht="15" customHeight="1">
-      <c r="A36" s="10"/>
-      <c r="B36" s="42"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
-      <c r="G36" s="10"/>
-      <c r="I36" s="23"/>
-    </row>
-    <row r="37" spans="1:13" ht="15" customHeight="1">
-      <c r="A37" s="10"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="42"/>
-      <c r="D37" s="42"/>
-      <c r="G37" s="10"/>
-      <c r="I37" s="23"/>
-    </row>
-    <row r="38" spans="1:13" ht="15" customHeight="1">
-      <c r="A38" s="10"/>
-      <c r="B38" s="42"/>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42"/>
-      <c r="G38" s="10"/>
-      <c r="I38" s="23"/>
-    </row>
-    <row r="39" spans="1:13" ht="15" customHeight="1">
-      <c r="A39" s="10"/>
-      <c r="B39" s="42"/>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42"/>
-      <c r="I39" s="23"/>
-    </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1">
-      <c r="A40" s="10"/>
-      <c r="B40" s="42"/>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42"/>
-      <c r="I40" s="23"/>
-    </row>
-    <row r="41" spans="1:13" ht="15" customHeight="1">
-      <c r="A41" s="10"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
-      <c r="I41" s="23"/>
-    </row>
-    <row r="42" spans="1:13" ht="15" customHeight="1">
-      <c r="A42" s="10"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="42"/>
-      <c r="I42" s="23"/>
-    </row>
-    <row r="43" spans="1:13" ht="15" customHeight="1">
-      <c r="A43" s="10"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42"/>
-      <c r="I43" s="23"/>
-    </row>
-    <row r="44" spans="1:13" ht="15" customHeight="1">
-      <c r="A44" s="10"/>
-      <c r="B44" s="42"/>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42"/>
-      <c r="I44" s="23"/>
-    </row>
-    <row r="45" spans="1:13" ht="15" customHeight="1">
-      <c r="A45" s="10"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="I45" s="23"/>
-    </row>
-    <row r="46" spans="1:13" ht="15" customHeight="1">
-      <c r="A46" s="10"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="I46" s="23"/>
-    </row>
-    <row r="47" spans="1:13" ht="15" customHeight="1">
-      <c r="A47" s="10"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="42"/>
-      <c r="D47" s="42"/>
-      <c r="I47" s="23"/>
-    </row>
-    <row r="48" spans="1:13" ht="15" customHeight="1">
-      <c r="A48" s="43"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="31"/>
-      <c r="I48" s="44"/>
+      <c r="G31" s="9"/>
+    </row>
+    <row r="34" spans="1:9" ht="15" customHeight="1">
+      <c r="A34" s="9"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="G34" s="9"/>
+      <c r="I34" s="18"/>
+    </row>
+    <row r="35" spans="1:9" ht="15" customHeight="1">
+      <c r="A35" s="9"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="G35" s="9"/>
+      <c r="I35" s="18"/>
+    </row>
+    <row r="36" spans="1:9" ht="15" customHeight="1">
+      <c r="A36" s="9"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="G36" s="9"/>
+      <c r="I36" s="18"/>
+    </row>
+    <row r="37" spans="1:9" ht="15" customHeight="1">
+      <c r="A37" s="9"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="G37" s="9"/>
+      <c r="I37" s="18"/>
+    </row>
+    <row r="38" spans="1:9" ht="15" customHeight="1">
+      <c r="A38" s="9"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="G38" s="9"/>
+      <c r="I38" s="18"/>
+    </row>
+    <row r="39" spans="1:9" ht="15" customHeight="1">
+      <c r="A39" s="9"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="I39" s="18"/>
+    </row>
+    <row r="40" spans="1:9" ht="15" customHeight="1">
+      <c r="A40" s="9"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="I40" s="18"/>
+    </row>
+    <row r="41" spans="1:9" ht="15" customHeight="1">
+      <c r="A41" s="9"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="I41" s="18"/>
+    </row>
+    <row r="42" spans="1:9" ht="15" customHeight="1">
+      <c r="A42" s="9"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="I42" s="18"/>
+    </row>
+    <row r="43" spans="1:9" ht="15" customHeight="1">
+      <c r="A43" s="9"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="I43" s="18"/>
+    </row>
+    <row r="44" spans="1:9" ht="15" customHeight="1">
+      <c r="A44" s="9"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="I44" s="18"/>
+    </row>
+    <row r="45" spans="1:9" ht="15" customHeight="1">
+      <c r="A45" s="9"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="I45" s="18"/>
+    </row>
+    <row r="46" spans="1:9" ht="15" customHeight="1">
+      <c r="A46" s="9"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="I46" s="18"/>
+    </row>
+    <row r="47" spans="1:9" ht="15" customHeight="1">
+      <c r="A47" s="9"/>
+      <c r="B47" s="34"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="I47" s="18"/>
+    </row>
+    <row r="48" spans="1:9" ht="15" customHeight="1">
+      <c r="A48" s="35"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="25"/>
+      <c r="I48" s="36"/>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1">
-      <c r="A49" s="43"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="31"/>
-      <c r="I49" s="44"/>
+      <c r="A49" s="35"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="25"/>
+      <c r="I49" s="36"/>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1">
-      <c r="A50" s="43"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="31"/>
-      <c r="I50" s="44"/>
+      <c r="A50" s="35"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="25"/>
+      <c r="I50" s="36"/>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1">
-      <c r="A51" s="43"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="31"/>
-      <c r="I51" s="44"/>
+      <c r="A51" s="35"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="25"/>
+      <c r="I51" s="36"/>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1">
-      <c r="A52" s="43"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="31"/>
-      <c r="I52" s="44"/>
+      <c r="A52" s="35"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="25"/>
+      <c r="I52" s="36"/>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1">
-      <c r="A53" s="43"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="31"/>
-      <c r="I53" s="44"/>
+      <c r="A53" s="35"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="25"/>
+      <c r="I53" s="36"/>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1">
-      <c r="A54" s="43"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="31"/>
-      <c r="I54" s="44"/>
+      <c r="A54" s="35"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="25"/>
+      <c r="I54" s="36"/>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1">
-      <c r="A55" s="43"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="31"/>
-      <c r="I55" s="44"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="25"/>
+      <c r="I55" s="36"/>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1">
-      <c r="A56" s="43"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="31"/>
-      <c r="I56" s="44"/>
+      <c r="A56" s="35"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="25"/>
+      <c r="I56" s="36"/>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1">
-      <c r="A57" s="43"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="31"/>
-      <c r="I57" s="44"/>
+      <c r="A57" s="35"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="25"/>
+      <c r="I57" s="36"/>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1">
-      <c r="A58" s="43"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="31"/>
-      <c r="I58" s="44"/>
+      <c r="A58" s="35"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="25"/>
+      <c r="I58" s="36"/>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1">
-      <c r="A59" s="43"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="31"/>
-      <c r="I59" s="44"/>
+      <c r="A59" s="35"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="25"/>
+      <c r="I59" s="36"/>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1">
-      <c r="A60" s="43"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="31"/>
-      <c r="I60" s="44"/>
+      <c r="A60" s="35"/>
+      <c r="B60" s="24"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="25"/>
+      <c r="I60" s="36"/>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1">
-      <c r="A61" s="43"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="31"/>
-      <c r="I61" s="44"/>
+      <c r="A61" s="35"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="25"/>
+      <c r="I61" s="36"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1">
-      <c r="A62" s="43"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="31"/>
-      <c r="I62" s="44"/>
+      <c r="A62" s="35"/>
+      <c r="B62" s="24"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="25"/>
+      <c r="I62" s="36"/>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1">
-      <c r="A63" s="43"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="31"/>
-      <c r="I63" s="44"/>
+      <c r="A63" s="35"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="25"/>
+      <c r="I63" s="36"/>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1">
-      <c r="A64" s="43"/>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="31"/>
-      <c r="I64" s="44"/>
+      <c r="A64" s="35"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="25"/>
+      <c r="I64" s="36"/>
     </row>
     <row r="65" spans="1:9" ht="15" customHeight="1">
-      <c r="A65" s="43"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="30"/>
-      <c r="D65" s="31"/>
-      <c r="I65" s="44"/>
+      <c r="A65" s="35"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="25"/>
+      <c r="I65" s="36"/>
     </row>
     <row r="66" spans="1:9" ht="15" customHeight="1">
-      <c r="A66" s="43"/>
-      <c r="B66" s="30"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="31"/>
-      <c r="I66" s="44"/>
+      <c r="A66" s="35"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="25"/>
+      <c r="I66" s="36"/>
     </row>
     <row r="67" spans="1:9" ht="15" customHeight="1">
-      <c r="A67" s="43"/>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="31"/>
-      <c r="I67" s="44"/>
+      <c r="A67" s="35"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="25"/>
+      <c r="I67" s="36"/>
     </row>
     <row r="68" spans="1:9" ht="15" customHeight="1">
-      <c r="A68" s="43"/>
-      <c r="B68" s="30"/>
-      <c r="C68" s="30"/>
-      <c r="D68" s="31"/>
-      <c r="I68" s="44"/>
+      <c r="A68" s="35"/>
+      <c r="B68" s="24"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="25"/>
+      <c r="I68" s="36"/>
     </row>
     <row r="69" spans="1:9" ht="15" customHeight="1">
-      <c r="A69" s="43"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="31"/>
-      <c r="I69" s="44"/>
+      <c r="A69" s="35"/>
+      <c r="B69" s="24"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="25"/>
+      <c r="I69" s="36"/>
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1">
-      <c r="A70" s="43"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="31"/>
-      <c r="I70" s="44"/>
+      <c r="A70" s="35"/>
+      <c r="B70" s="24"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="25"/>
+      <c r="I70" s="36"/>
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1">
-      <c r="A71" s="43"/>
-      <c r="B71" s="30"/>
-      <c r="C71" s="30"/>
-      <c r="D71" s="31"/>
-      <c r="I71" s="44"/>
+      <c r="A71" s="35"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="25"/>
+      <c r="I71" s="36"/>
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1">
-      <c r="A72" s="43"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="30"/>
-      <c r="D72" s="31"/>
-      <c r="I72" s="44"/>
+      <c r="A72" s="35"/>
+      <c r="B72" s="24"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="25"/>
+      <c r="I72" s="36"/>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1">
-      <c r="A73" s="43"/>
-      <c r="B73" s="30"/>
-      <c r="C73" s="30"/>
-      <c r="D73" s="31"/>
-      <c r="I73" s="44"/>
+      <c r="A73" s="35"/>
+      <c r="B73" s="24"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="25"/>
+      <c r="I73" s="36"/>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1">
-      <c r="A74" s="43"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="31"/>
-      <c r="I74" s="44"/>
+      <c r="A74" s="35"/>
+      <c r="B74" s="24"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="25"/>
+      <c r="I74" s="36"/>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1">
-      <c r="A75" s="43"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="31"/>
-      <c r="I75" s="44"/>
+      <c r="A75" s="35"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="25"/>
+      <c r="I75" s="36"/>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1">
-      <c r="A76" s="43"/>
-      <c r="B76" s="30"/>
-      <c r="C76" s="30"/>
-      <c r="D76" s="31"/>
-      <c r="I76" s="44"/>
+      <c r="A76" s="35"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="25"/>
+      <c r="I76" s="36"/>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1">
-      <c r="A77" s="43"/>
-      <c r="B77" s="30"/>
-      <c r="C77" s="30"/>
-      <c r="D77" s="31"/>
-      <c r="I77" s="44"/>
+      <c r="A77" s="35"/>
+      <c r="B77" s="24"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="25"/>
+      <c r="I77" s="36"/>
     </row>
     <row r="78" spans="1:9" ht="15" customHeight="1">
-      <c r="A78" s="43"/>
-      <c r="B78" s="30"/>
-      <c r="C78" s="30"/>
-      <c r="D78" s="31"/>
-      <c r="I78" s="44"/>
+      <c r="A78" s="35"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="25"/>
+      <c r="I78" s="36"/>
     </row>
     <row r="79" spans="1:9" ht="15" customHeight="1">
-      <c r="A79" s="43"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="31"/>
-      <c r="I79" s="44"/>
+      <c r="A79" s="35"/>
+      <c r="B79" s="24"/>
+      <c r="C79" s="24"/>
+      <c r="D79" s="25"/>
+      <c r="I79" s="36"/>
     </row>
     <row r="80" spans="1:9" ht="15" customHeight="1">
-      <c r="A80" s="43"/>
-      <c r="B80" s="30"/>
-      <c r="C80" s="30"/>
-      <c r="D80" s="31"/>
-      <c r="I80" s="44"/>
+      <c r="A80" s="35"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="25"/>
+      <c r="I80" s="36"/>
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1">
-      <c r="A81" s="43"/>
-      <c r="B81" s="30"/>
-      <c r="C81" s="30"/>
-      <c r="D81" s="31"/>
-      <c r="I81" s="44"/>
+      <c r="A81" s="35"/>
+      <c r="B81" s="24"/>
+      <c r="C81" s="24"/>
+      <c r="D81" s="25"/>
+      <c r="I81" s="36"/>
     </row>
     <row r="82" spans="1:9" ht="15" customHeight="1">
-      <c r="A82" s="43"/>
-      <c r="B82" s="30"/>
-      <c r="C82" s="30"/>
-      <c r="D82" s="31"/>
-      <c r="I82" s="44"/>
+      <c r="A82" s="35"/>
+      <c r="B82" s="24"/>
+      <c r="C82" s="24"/>
+      <c r="D82" s="25"/>
+      <c r="I82" s="36"/>
     </row>
     <row r="83" spans="1:9" ht="15" customHeight="1">
-      <c r="A83" s="43"/>
-      <c r="B83" s="30"/>
-      <c r="C83" s="30"/>
-      <c r="D83" s="31"/>
-      <c r="I83" s="44"/>
+      <c r="A83" s="35"/>
+      <c r="B83" s="24"/>
+      <c r="C83" s="24"/>
+      <c r="D83" s="25"/>
+      <c r="I83" s="36"/>
     </row>
     <row r="84" spans="1:9" ht="15" customHeight="1">
-      <c r="A84" s="43"/>
-      <c r="B84" s="30"/>
-      <c r="C84" s="30"/>
-      <c r="D84" s="31"/>
-      <c r="I84" s="44"/>
+      <c r="A84" s="35"/>
+      <c r="B84" s="24"/>
+      <c r="C84" s="24"/>
+      <c r="D84" s="25"/>
+      <c r="I84" s="36"/>
     </row>
     <row r="85" spans="1:9" ht="15" customHeight="1">
-      <c r="A85" s="43"/>
-      <c r="B85" s="30"/>
-      <c r="C85" s="30"/>
-      <c r="D85" s="31"/>
-      <c r="I85" s="44"/>
+      <c r="A85" s="35"/>
+      <c r="B85" s="24"/>
+      <c r="C85" s="24"/>
+      <c r="D85" s="25"/>
+      <c r="I85" s="36"/>
     </row>
     <row r="86" spans="1:9" ht="15" customHeight="1">
-      <c r="A86" s="43"/>
-      <c r="B86" s="30"/>
-      <c r="C86" s="30"/>
-      <c r="D86" s="31"/>
-      <c r="I86" s="44"/>
+      <c r="A86" s="35"/>
+      <c r="B86" s="24"/>
+      <c r="C86" s="24"/>
+      <c r="D86" s="25"/>
+      <c r="I86" s="36"/>
     </row>
     <row r="87" spans="1:9" ht="15" customHeight="1">
-      <c r="A87" s="43"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="31"/>
-      <c r="I87" s="44"/>
+      <c r="A87" s="35"/>
+      <c r="B87" s="24"/>
+      <c r="C87" s="24"/>
+      <c r="D87" s="25"/>
+      <c r="I87" s="36"/>
     </row>
     <row r="88" spans="1:9" ht="15" customHeight="1">
-      <c r="A88" s="43"/>
-      <c r="B88" s="30"/>
-      <c r="C88" s="30"/>
-      <c r="D88" s="31"/>
-      <c r="I88" s="44"/>
+      <c r="A88" s="35"/>
+      <c r="B88" s="24"/>
+      <c r="C88" s="24"/>
+      <c r="D88" s="25"/>
+      <c r="I88" s="36"/>
     </row>
     <row r="89" spans="1:9" ht="15" customHeight="1">
-      <c r="A89" s="43"/>
-      <c r="B89" s="30"/>
-      <c r="C89" s="30"/>
-      <c r="D89" s="31"/>
-      <c r="I89" s="44"/>
+      <c r="A89" s="35"/>
+      <c r="B89" s="24"/>
+      <c r="C89" s="24"/>
+      <c r="D89" s="25"/>
+      <c r="I89" s="36"/>
     </row>
     <row r="90" spans="1:9" ht="15" customHeight="1">
-      <c r="A90" s="43"/>
-      <c r="B90" s="30"/>
-      <c r="C90" s="30"/>
-      <c r="D90" s="31"/>
-      <c r="I90" s="44"/>
+      <c r="A90" s="35"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="24"/>
+      <c r="D90" s="25"/>
+      <c r="I90" s="36"/>
     </row>
     <row r="91" spans="1:9" ht="15" customHeight="1">
-      <c r="A91" s="43"/>
-      <c r="B91" s="30"/>
-      <c r="C91" s="30"/>
-      <c r="D91" s="31"/>
-      <c r="I91" s="44"/>
+      <c r="A91" s="35"/>
+      <c r="B91" s="24"/>
+      <c r="C91" s="24"/>
+      <c r="D91" s="25"/>
+      <c r="I91" s="36"/>
     </row>
     <row r="92" spans="1:9" ht="15" customHeight="1">
-      <c r="A92" s="43"/>
-      <c r="B92" s="30"/>
-      <c r="C92" s="30"/>
-      <c r="D92" s="31"/>
-      <c r="I92" s="44"/>
+      <c r="A92" s="35"/>
+      <c r="B92" s="24"/>
+      <c r="C92" s="24"/>
+      <c r="D92" s="25"/>
+      <c r="I92" s="36"/>
     </row>
     <row r="93" spans="1:9" ht="15" customHeight="1">
-      <c r="A93" s="43"/>
-      <c r="B93" s="30"/>
-      <c r="C93" s="30"/>
-      <c r="D93" s="31"/>
-      <c r="I93" s="44"/>
+      <c r="A93" s="35"/>
+      <c r="B93" s="24"/>
+      <c r="C93" s="24"/>
+      <c r="D93" s="25"/>
+      <c r="I93" s="36"/>
     </row>
     <row r="94" spans="1:9" ht="15" customHeight="1">
-      <c r="A94" s="43"/>
-      <c r="B94" s="30"/>
-      <c r="C94" s="30"/>
-      <c r="D94" s="31"/>
-      <c r="I94" s="44"/>
+      <c r="A94" s="35"/>
+      <c r="B94" s="24"/>
+      <c r="C94" s="24"/>
+      <c r="D94" s="25"/>
+      <c r="I94" s="36"/>
     </row>
     <row r="95" spans="1:9" ht="15" customHeight="1">
-      <c r="A95" s="43"/>
-      <c r="B95" s="30"/>
-      <c r="C95" s="30"/>
-      <c r="D95" s="31"/>
-      <c r="I95" s="44"/>
+      <c r="A95" s="35"/>
+      <c r="B95" s="24"/>
+      <c r="C95" s="24"/>
+      <c r="D95" s="25"/>
+      <c r="I95" s="36"/>
     </row>
     <row r="96" spans="1:9" ht="15" customHeight="1">
-      <c r="A96" s="43"/>
-      <c r="B96" s="30"/>
-      <c r="C96" s="30"/>
-      <c r="D96" s="31"/>
-      <c r="I96" s="44"/>
+      <c r="A96" s="35"/>
+      <c r="B96" s="24"/>
+      <c r="C96" s="24"/>
+      <c r="D96" s="25"/>
+      <c r="I96" s="36"/>
     </row>
     <row r="97" spans="1:9" ht="15" customHeight="1">
-      <c r="A97" s="43"/>
-      <c r="B97" s="30"/>
-      <c r="C97" s="30"/>
-      <c r="D97" s="31"/>
-      <c r="I97" s="44"/>
+      <c r="A97" s="35"/>
+      <c r="B97" s="24"/>
+      <c r="C97" s="24"/>
+      <c r="D97" s="25"/>
+      <c r="I97" s="36"/>
     </row>
     <row r="98" spans="1:9" ht="15" customHeight="1">
-      <c r="A98" s="43"/>
-      <c r="B98" s="30"/>
-      <c r="C98" s="30"/>
-      <c r="D98" s="31"/>
-      <c r="I98" s="44"/>
+      <c r="A98" s="35"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="25"/>
+      <c r="I98" s="36"/>
     </row>
     <row r="99" spans="1:9" ht="15" customHeight="1">
-      <c r="A99" s="43"/>
-      <c r="B99" s="30"/>
-      <c r="C99" s="30"/>
-      <c r="D99" s="31"/>
-      <c r="I99" s="44"/>
+      <c r="A99" s="35"/>
+      <c r="B99" s="24"/>
+      <c r="C99" s="24"/>
+      <c r="D99" s="25"/>
+      <c r="I99" s="36"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <mergeCells count="9">
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="A8" r:id="rId1" xr:uid="{15559E83-5E49-4C79-96A1-004F2D5681B1}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" scale="66" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="82" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="9" max="1048575" man="1"/>
-  </colBreaks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>